--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:04:00+00:00</t>
+    <t>2025-02-17T11:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:54+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1577,7 +1577,7 @@
     <t>PSSFeedbackModel.outcome</t>
   </si>
   <si>
-    <t>accepted, discarded, overridden</t>
+    <t>accepted, rejected, overridden</t>
   </si>
   <si>
     <t>PSSFeedbackModel.suggestionOutcome</t>
@@ -1604,13 +1604,13 @@
     <t>PSSFeedbackModel.suggestionOutcome.outcome</t>
   </si>
   <si>
-    <t>accepted or overridden</t>
+    <t>accepted, rejected or overridden</t>
   </si>
   <si>
     <t>PSSFeedbackModel.suggestionOutcome.overrideReason</t>
   </si>
   <si>
-    <t>The reason for overriding - code or text</t>
+    <t>The reason for rejecting or overriding - code or text</t>
   </si>
   <si>
     <t>PSSMedicationRequest</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
